--- a/data/describe/few_shot/cluster/messages_personality.xlsx
+++ b/data/describe/few_shot/cluster/messages_personality.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\input_cluster\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\cluster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AEF3173-F82C-461B-8329-4F7803BA5A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF3A8C4-F7B2-4EFA-A568-B42C4128AAE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34935" yWindow="1470" windowWidth="33900" windowHeight="15465" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="52080" yWindow="2235" windowWidth="26655" windowHeight="17070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>User</t>
   </si>
@@ -177,40 +177,38 @@
     <t>When a person is described as stable, it means that they tend to maintain a steady demeanor and don't frequently shift their emotions. While they may experience some fluctuations, they generally exhibit a consistent and reliable nature that makes them dependable and trustworthy.</t>
   </si>
   <si>
-    <t xml:space="preserve">Now your task is to provide a description of a cluster.
-You will receive information about the cluster based on the latent factors that best describe it.
-For each cluster, write a concise summary based on the available information.
+    <t>Members of this cluster can be described as vibrant and spirited, with a tendency towards spontaneity and creativity. The cluster's specific strengths lie in their liveliness, carefree attitude, and inventive nature, which enables them to approach situations with enthusiasm and originality. However, they exhibit weaknesses in sensitivity and care, often coming across as careless and less adaptable, suggesting a need for greater emotional awareness and stability in their interactions.</t>
+  </si>
+  <si>
+    <t>This cluster is characterized by individuals who balance engagement with thoughtfulness while exhibiting stability and care. Their strengths lie in being proactive and attentive to concerns, along with a stable demeanor and gentle nature, which fosters strong interpersonal relationships. However, the cluster may struggle with flexibility and spontaneity, as well as a formal approach that may limit their adaptability in dynamic situations.</t>
+  </si>
+  <si>
+    <t>This cluster consists of individuals who are characterized by their sociable nature and spontaneity, embracing a vibrant and lively approach to life. Their specific strengths lie in their carefree and proactive attitude, as well as their strong commitment to organizing tasks, making them effective collaborators in social and team settings. However, this cluster may face challenges in areas such as articulation and complexity of thought, as they tend to be less imaginative and struggle with depth in communication.</t>
+  </si>
+  <si>
+    <t>This cluster consists of individuals who display a balanced mix of engagement and organization, though they tend toward lower sensitivity and creativity. Their strengths lie in being organized and committed, allowing them to reliably manage tasks while maintaining a lively and articulate demeanor. However, they may struggle with personal connections due to their lower levels of sensitivity, thoughtfulness, and gentle caring, which could affect their interpersonal relationships.</t>
+  </si>
+  <si>
+    <t>This cluster is characterized by individuals who are generally sociable and engaging, suggesting a strong interpersonal connection with others. Their strengths lie in their sociability, empathy, and commitment to organization, which likely enables them to work well in team settings and foster positive relationships. However, they may struggle with discretion and diligence, as well as a tendency to be slightly less caring, which could impact their professional and personal interactions.</t>
+  </si>
+  <si>
+    <t>Thats really good. You truly understand the factors and names. 
+Now your task is to provide a description of a cluster.
+Please use the statistical description enclosed with ``` ´´´ . It provides information about the cluster based on the latent factors that most accurately describe it.For each cluster, write a concise summary based on the available information.
 The first sentence should give an overview of the cluster. 
 The second sentence should describe the cluster’s specific strengths based on the available information.
 The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-I will provided you with the cluster description and you will return the summary. </t>
-  </si>
-  <si>
-    <t>Understood. Please provide the cluster descriptions.</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster:```Members of this cluster can be described as:  slightly low on sensitive and private,  slightly high on carefree and spontaneous,  relatively high on lively and careless,  normal on articulate and complex,  slightly low on disinterested and calm,  relatively low on flexible and casual,  slightly high on creative and inventive,  relatively low on unimaginative,  relatively low on unprepared,  normal on not unsettled,  slightly high on not gentle and caring,  slightly low on not variable```</t>
-  </si>
-  <si>
-    <t>Members of this cluster can be described as vibrant and spirited, with a tendency towards spontaneity and creativity. The cluster's specific strengths lie in their liveliness, carefree attitude, and inventive nature, which enables them to approach situations with enthusiasm and originality. However, they exhibit weaknesses in sensitivity and care, often coming across as careless and less adaptable, suggesting a need for greater emotional awareness and stability in their interactions.</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster:```Members of this cluster can be described as:  normal on sociable and engaging,  normal on carefree and spontaneous,  normal on discreet and diligent,  normal on articulate and complex,  relatively high on concerned and proactive,  relatively low on flexible and casual,  normal on literal and formal,  relatively high on abstract,  slightly high on prepared,  normal on not unsettled,  normal on gentle and caring,  relatively high on stable```</t>
-  </si>
-  <si>
-    <t>This cluster is characterized by individuals who balance engagement with thoughtfulness while exhibiting stability and care. Their strengths lie in being proactive and attentive to concerns, along with a stable demeanor and gentle nature, which fosters strong interpersonal relationships. However, the cluster may struggle with flexibility and spontaneity, as well as a formal approach that may limit their adaptability in dynamic situations.</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster:```Members of this cluster can be described as:  relatively high on sociable and engaging,  extremely high on carefree and spontaneous,  extremely high on lively and careless,  slightly low on articulate and complex,  extremely high on concerned and proactive,  extremely high on organized and committed,  normal on literal and formal,  extremely low on unimaginative,  relatively high on prepared,  normal on not unsettled,  normal on gentle and caring,  relatively high on stable```</t>
-  </si>
-  <si>
-    <t>This cluster consists of individuals who are characterized by their sociable nature and spontaneity, embracing a vibrant and lively approach to life. Their specific strengths lie in their carefree and proactive attitude, as well as their strong commitment to organizing tasks, making them effective collaborators in social and team settings. However, this cluster may face challenges in areas such as articulation and complexity of thought, as they tend to be less imaginative and struggle with depth in communication.</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster:```Members of this cluster can be described as:  relatively low on sensitive and private,  relatively low on thoughtful and imaginative,  normal on lively and careless,  normal on articulate and complex,  normal on disinterested and calm,  slightly high on organized and committed,  normal on creative and inventive,  slightly low on unimaginative,  normal on prepared,  slightly low on unsettled,  relatively low on gentle and caring,  normal on stable```</t>
-  </si>
-  <si>
-    <t>This cluster consists of individuals who display a balanced mix of engagement and organization, though they tend toward lower sensitivity and creativity. Their strengths lie in being organized and committed, allowing them to reliably manage tasks while maintaining a lively and articulate demeanor. However, they may struggle with personal connections due to their lower levels of sensitivity, thoughtfulness, and gentle caring, which could affect their interpersonal relationships.</t>
+I will provided you with the cluster description and you will return the summary. 
+Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster:```Members of this cluster can be described as:  slightly low on sensitive and private,  slightly high on carefree and spontaneous,  relatively high on lively and careless,  normal on articulate and complex,  slightly low on disinterested and calm,  relatively low on flexible and casual,  slightly high on creative and inventive,  relatively low on unimaginative,  relatively low on unprepared,  normal on not unsettled,  slightly high on not gentle and caring,  slightly low on not variable´´´</t>
+  </si>
+  <si>
+    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster:```Members of this cluster can be described as:  normal on sociable and engaging,  normal on carefree and spontaneous,  normal on discreet and diligent,  normal on articulate and complex,  relatively high on concerned and proactive,  relatively low on flexible and casual,  normal on literal and formal,  relatively high on abstract,  slightly high on prepared,  normal on not unsettled,  normal on gentle and caring,  relatively high on stable´´´</t>
+  </si>
+  <si>
+    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster:```Members of this cluster can be described as:  relatively high on sociable and engaging,  extremely high on carefree and spontaneous,  extremely high on lively and careless,  slightly low on articulate and complex,  extremely high on concerned and proactive,  extremely high on organized and committed,  normal on literal and formal,  extremely low on unimaginative,  relatively high on prepared,  normal on not unsettled,  normal on gentle and caring,  relatively high on stable´´´</t>
+  </si>
+  <si>
+    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster:```Members of this cluster can be described as:  relatively low on sensitive and private,  relatively low on thoughtful and imaginative,  normal on lively and careless,  normal on articulate and complex,  normal on disinterested and calm,  slightly high on organized and committed,  normal on creative and inventive,  slightly low on unimaginative,  normal on prepared,  slightly low on unsettled,  relatively low on gentle and caring,  normal on stable´´´</t>
   </si>
   <si>
     <t>Those were really good. Exactly what I am looking for. 
@@ -221,10 +219,7 @@
 The first sentence should give an overview of the cluster. 
 The second sentence should describe the cluster’s specific strengths based on the available information.
 The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-Now do the same thing with the following: ```Members of this cluster can be described as:  relatively high on sociable and engaging,  normal on thoughtful and imaginative,  slightly low on discreet and diligent,  slightly high on empathetic and straightforward,  normal on disinterested and calm,  relatively high on organized and committed,  normal on literal and formal,  normal on abstract,  normal on unprepared,  normal on not unsettled,  slightly high on not gentle and caring,  slightly low on not variable```</t>
-  </si>
-  <si>
-    <t>This cluster is characterized by individuals who are generally sociable and engaging, suggesting a strong interpersonal connection with others. Their strengths lie in their sociability, empathy, and commitment to organization, which likely enables them to work well in team settings and foster positive relationships. However, they may struggle with discretion and diligence, as well as a tendency to be slightly less caring, which could impact their professional and personal interactions.</t>
+Now do the same thing with the following: ```Members of this cluster can be described as:  relatively high on sociable and engaging,  normal on thoughtful and imaginative,  slightly low on discreet and diligent,  slightly high on empathetic and straightforward,  normal on disinterested and calm,  relatively high on organized and committed,  normal on literal and formal,  normal on abstract,  normal on unprepared,  normal on not unsettled,  slightly high on not gentle and caring,  slightly low on not variable´´´</t>
   </si>
 </sst>
 </file>
@@ -280,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -290,6 +285,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -593,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="76.36328125" style="2" customWidth="1"/>
@@ -800,52 +798,44 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
+    <row r="26" spans="1:2" ht="261" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="2" t="s">
+    </row>
+    <row r="27" spans="1:2" ht="102.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
+    <row r="28" spans="1:2" ht="116" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="2" t="s">
+    </row>
+    <row r="29" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
+    <row r="30" spans="1:2" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="174" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/data/describe/few_shot/cluster/messages_personality.xlsx
+++ b/data/describe/few_shot/cluster/messages_personality.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\cluster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{D2EC6052-09C1-4178-A088-0B6158426A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0C869D-EFC7-4845-A54C-23BC3F23AE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30675" yWindow="1815" windowWidth="19455" windowHeight="16800"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="messages_personality1.xlsx" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>User</t>
   </si>
@@ -33,188 +33,101 @@
     <t>Assistant</t>
   </si>
   <si>
-    <t>What does it mean when a person is described as private and sensitive?</t>
-  </si>
-  <si>
-    <t>Someone who is private and sensitive might find themselves easily irritated, preferring to keep to themselves and showing little interest in others. This person also tends to feel blue and can get upset quite easily.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as social and engaging?</t>
-  </si>
-  <si>
-    <t>A social and engaging person absolutely thrives in company, effortlessly feeling comfortable around people and striking up conversations with many at parties. They love to kick off discussions, often becoming the heart of the party, and genuinely enjoy learning about others.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as meticulous and inventive?</t>
-  </si>
-  <si>
-    <t>A meticulous and inventive person is absolutely bursting with excellent ideas and possesses a truly vivid imagination, often found brimming with new thoughts. They tend to worry about things and pay careful attention to all the little details.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as broad-minded and practical?</t>
-  </si>
-  <si>
-    <t>A person described as broad-minded and practical is not one to fret over things, nor do they often get lost in a vivid imagination or constantly burst forth with new concepts. Instead, they tend to be less focused on generating brilliant ideas or getting caught up in the minutiae of details.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as humble and orderly?</t>
-  </si>
-  <si>
-    <t>Humble and orderly individuals prefer to stay out of the spotlight, getting their chores done promptly, and maintaining a calm demeanor, especially when meeting new people. They also make a point of taking time out for others, demonstrating a considerate and composed nature.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as exuberant and direct?</t>
-  </si>
-  <si>
-    <t>When a person is described as exuberant and direct, they are often the life of the party and aren't afraid to speak their mind, even if it means occasionally insulting someone. You might also notice they have a habit of forgetting to put things back in their place, leaving belongings scattered, and generally making a bit of a mess.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as intellectual and expressive?</t>
-  </si>
-  <si>
-    <t>A person described as intellectual and expressive boasts a rich vocabulary, often utilizing difficult words to articulate their abundant ideas and quickly grasp new concepts. They are full of innovative thoughts, though their focus on ideas might mean they aren't always deeply interested in the feelings or experiences of others.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as empathetic and concrete?</t>
-  </si>
-  <si>
-    <t>An empathetic and concrete person truly feels and sympathizes with the emotions of others, always ready to take time out to help. They tend to shy away from abstract concepts, preferring to focus on practical, real-world ideas.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as self-possessed and systematic?</t>
-  </si>
-  <si>
-    <t>A self-possessed and systematic individual often comes across as quite relaxed, showing little interest in others or their problems. They are also known for liking order and are comfortable initiating conversations.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as thoughtful and vigilant?</t>
-  </si>
-  <si>
-    <t>When a person is described as thoughtful and vigilant, it means they are often someone who finds themselves wrapped up in worrying about various matters.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as easygoing and casual?</t>
-  </si>
-  <si>
-    <t>An easygoing and casual person might often forget where things go, leading to a bit of a mess and belongings left scattered around. They generally carry a relaxed demeanor, though they might occasionally shirk their duties.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as planned and prepared?</t>
-  </si>
-  <si>
-    <t>A person who is planned and prepared loves to stick to a schedule and tackles their chores without delay. They are also the kind of individual who is always ready for whatever comes their way.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as articulate and literal?</t>
-  </si>
-  <si>
-    <t>Someone described as articulate and literal possesses a rich vocabulary and enjoys using complex words to express themselves. Yet, when it comes to creativity, their imagination isn't particularly strong.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as imaginative and conceptual?</t>
-  </si>
-  <si>
-    <t>Someone who is imaginative and conceptual is truly a fount of creativity, always bubbling with a vivid imagination. They are also brimming with excellent and fresh ideas, constantly generating new thoughts and concepts.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as speculative and spontaneous?</t>
-  </si>
-  <si>
-    <t>A speculative and spontaneous person doesn't shy away from abstract ideas, finding them easy to understand and being genuinely interested in them, and they often possess a good imagination. You won't find them rigidly sticking to a schedule, as they prefer a more flexible approach to life.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as observant and routine?</t>
-  </si>
-  <si>
-    <t>When a person is described as observant and routine, they might find abstract ideas a bit of a puzzle and aren't typically known for a wild imagination. Instead, they prefer the comfort of sticking to a clear schedule and generally aren't very interested in exploring complex, abstract concepts.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as impromptu and bold?</t>
-  </si>
-  <si>
-    <t>When a person is described as impromptu and bold, it means they are not always prepared for what's ahead.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as foresighted and cautious?</t>
-  </si>
-  <si>
-    <t>When a person is described as foresighted and cautious, it means they are the kind of individual who is always prepared for what lies ahead.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as impressionable and reactive?</t>
-  </si>
-  <si>
-    <t>When a person is described as impressionable and reactive, it means they tend to be quite easily disturbed by things.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as unflappable and stable?</t>
-  </si>
-  <si>
-    <t>When a person is described as unflappable and stable, it means they are not easily disturbed by external events and maintain a calm demeanor even in challenging situations. This reliability suggests they approach life with a sense of consistency and steadiness, making them a soothing presence to those around them.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as kindly and warm?</t>
-  </si>
-  <si>
-    <t>When a person is described as kindly and warm, it means they tend to have a gentle and compassionate nature, showing care for othersâ€”even if those traits are not predominantly defined by strong characteristics. In contrast, they are not firm and objective, suggesting they may prioritize empathy and understanding over strictness or detachment.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as firm and objective?</t>
-  </si>
-  <si>
-    <t>When a person is described as firm and objective, it means they are not kindly and warm. They tend to approach situations with a level-headed and logical perspective, often making decisions based on facts rather than emotions, and can be unwavering in their stance.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as even temper?</t>
-  </si>
-  <si>
-    <t>When a person is described as having an even temper, it means they are not prone to mood swings or emotional ups and downs. They maintain a steady and calm demeanor, remaining composed even in situations that might provoke strong feelings in others.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as variable temper?</t>
-  </si>
-  <si>
-    <t>When a person is described as having a variable temper, it means they often find their mood shifting unpredictably. This can make their emotional responses feel a bit like a rollercoaster, keeping others on their toes and unsure of what to expect from them.</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who are highly sociable, imaginatively conceptual, and remarkably stable, though they may experience some emotional fluctuations. Their strengths shine through in their strong social engagement, a rich and imaginative conceptual mind that generates fresh ideas, and a notably unflappable and stable demeanor that keeps them calm and consistent. They also possess a slight inclination towards being planned and prepared. However, a relative weakness lies in their less even temper, suggesting they may be more prone to mood swings, and despite their imagination, they also show a slight tendency towards being observant and routine, which might imply a subtle disconnect in fully embracing abstract concepts.</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who are often preoccupied with worries, generally less private, and tend to be quite responsible, though not always warm or even-tempered. Their strengths include a thoughtful and vigilant nature, indicating attentiveness to potential issues, coupled with a tendency to be more prepared and responsible rather than casual or impulsive. However, they exhibit weaknesses in being less private and sensitive, less humble or orderly in their interactions, less intellectually expressive, less kindly or warm, and are prone to a more variable temper.</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who are socially engaging and well-prepared, embodying a stable yet sometimes unpredictable demeanor, with a preference for practical rather than abstract thought. Their specific strengths include their high sociability and engaging nature, consistently being foresighted and cautious in preparation, and maintaining an unflappable and stable temperament, while also showing empathy and a preference for concrete ideas. However, they exhibit weaknesses in being prone to worrying, can struggle with abstract ideas and a vivid imagination, and are characterized by a relatively high variable temper, suggesting unpredictable mood shifts.</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who are sociable and well-organized, demonstrating a stable and prepared approach to life, though they are less inclined towards abstract thought or intense imagination. Their specific strengths include being socially engaging, empathetically concrete, humble and orderly, and reliably planned and prepared, all supported by an unflappable and even-tempered nature. However, they exhibit weaknesses in being less meticulous and inventive, showing less interest in speculative or spontaneous ideas, and while firm and objective, they are noted for not being particularly kindly and warm.</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who are highly social and meticulously prepared, driven by a thoughtful and vigilant nature, yet they grapple with emotional variability and a tendency towards direct, sometimes careless, exuberance. Their strengths are evident in their exceptional planning and preparedness, making them reliably ready for challenges, complemented by their social and engaging demeanor, kindly warmth, and unwavering stability. However, they exhibit notable weaknesses in their intellectual expression and creative spontaneity, often finding abstract ideas challenging and lacking an interest in others' deeper emotions, compounded by a highly variable temper that leads to unpredictable mood shifts and a tendency to be direct and somewhat careless in social settings.</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who are typically lively and imaginative, preferring to be at the center of attention, though they can also be prone to emotional fluctuations. Their key strengths lie in their high levels of exuberance and directness, making them the life of the party, coupled with a highly imaginative and conceptual mind that constantly generates fresh and excellent ideas. However, they exhibit weaknesses in being less self-possessed and systematic, often lacking order, and tending to be less kindly and warm, which is compounded by a slightly variable and unpredictable temper.</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster: ```Members of this cluster can be described as:  slightly high on social and engaging,  slightly low on meticulous and inventive,  normal on humble and orderly,  slightly high on empathetic and concrete,  normal on self-possessed and systematic,  slightly high on planned and prepared,  slightly low on articulate and literal,  slightly low on speculative and spontaneous,  normal on impromptu and bold,  relatively low on impressionable and reactive,  relatively high on firm and objective,  normal on even temper´´´</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster: ```Members of this cluster can be described as:  slightly high on social and engaging,  slightly high on broad-minded and practical,  slightly high on exuberant and direct,  normal on empathetic and concrete,  slightly high on thoughtful and vigilant,  relatively low on easygoing and casual,  normal on articulate and literal,  relatively high on observant and routine,  relatively high on foresighted and cautious,  slightly high on unflappable and stable,  normal on firm and objective,  relatively high on variable temper´´´</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster: ```Members of this cluster can be described as:  relatively low on private and sensitive,  normal on broad-minded and practical,  relatively low on humble and orderly,  slightly low on intellectual and expressive,  relatively high on thoughtful and vigilant,  slightly low on easygoing and casual,  normal on articulate and literal,  normal on speculative and spontaneous,  slightly low on impromptu and bold,  normal on impressionable and reactive,  slightly low on kindly and warm,  slightly low on even temper´´´</t>
+    <t>What does it mean when a person is described as sensitive and private?</t>
+  </si>
+  <si>
+    <t>When a person is described as sensitive and private, they often aren't very interested in others and can easily get irritated. These individuals also tend to be quiet, prefer to keep in the background around strangers, and generally have little to say.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as engaging and sociable?</t>
+  </si>
+  <si>
+    <t>When a person is described as engaging and sociable, it means they feel very comfortable around others, often taking the lead to start conversations and chat with many different people at parties. They are genuinely interested in the people around them and frequently become the life of the party.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as thoughtful and imaginative?</t>
+  </si>
+  <si>
+    <t>A thoughtful and imaginative person tends to worry about things and can get stressed out easily, often because they possess a very vivid imagination. They are truly brimming with excellent ideas and are constantly full of new thoughts.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as not anxious and carefree?</t>
+  </si>
+  <si>
+    <t>A person described as not anxious and carefree isn't prone to worrying or getting stressed out easily. They also don't tend to have a vivid imagination, excellent ideas, or be constantly full of new thoughts, indicating a more relaxed and less preoccupied state.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as discreet and diligent?</t>
+  </si>
+  <si>
+    <t>A discreet and diligent person strongly prefers to stay out of the limelight, making sure their chores are done right away, and always setting aside time for others. They also tend to be quiet when meeting new people and appreciate things being in their proper place.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as carefree and spontaneous?</t>
+  </si>
+  <si>
+    <t>A carefree and spontaneous person might occasionally insult others without much thought, and you'll often find their belongings scattered as they tend to forget putting things back or shirk their duties. However, they are also known for being the vibrant life of the party!</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as insightful and reserved?</t>
+  </si>
+  <si>
+    <t>A person described as insightful and reserved is often brimming with original thoughts and excellent ideas, often expressed with a rich vocabulary. While intellectually vibrant, they tend to keep to themselves, not showing much interest in other people's problems or feelings.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as empathetic and considerate?</t>
+  </si>
+  <si>
+    <t>When someone is described as empathetic and considerate, it means they truly feel and sympathize with the emotions of those around them. They are also known for taking the time to be there for others, offering their support and understanding.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as practical and grounded?</t>
+  </si>
+  <si>
+    <t>A practical and grounded person isn't particularly interested in abstract ideas and may find them hard to grasp, often coupled with not having a very vivid imagination. You'll find them relaxed most of the time, and they're usually the ones to start conversations.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as not practical and speculative?</t>
+  </si>
+  <si>
+    <t>A person described as not practical and speculative is someone who loves to dive into abstract ideas and possesses a good imagination. They easily grasp complex concepts and may not always be relaxed, often preferring others to initiate conversations.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as disorganized and laid-back?</t>
+  </si>
+  <si>
+    <t>When you describe someone as disorganized and laid-back, imagine a person who often creates a bit of a mess, frequently forgets to put things away, and has a habit of leaving their belongings scattered. They might even shirk their duties from time to time, but you'll usually find them quite relaxed and easygoing.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as organized and punctual?</t>
+  </si>
+  <si>
+    <t>When a person is described as organized and punctual, it means they have a knack for getting things done efficiently, often completing chores right away and sticking to a schedule. They approach life with a prepared mindset, ensuring they are always ready for what comes next!</t>
   </si>
   <si>
     <t>Thats really good. You truly understand the factors and names. 
 Now your task is to provide a description of a cluster.
-Please use the statistical description enclosed with ``` ´´´ .  It provides information about the cluster based on the latent factors that most accurately describe it.For each cluster, write a concise summary based on the available information.
+Please use the statistical description enclosed with ``` ´´´ . It provides information about the cluster based on the latent factors that most accurately describe it.
+Now your task is to provide a description of a cluster.
+You will receive information about the cluster based on the latent factors that best describe it.
+For each cluster, write a concise summary based on the available information.
 The first sentence should give an overview of the cluster. 
 The second sentence should describe the cluster’s specific strengths based on the available information.
 The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
 I will provided you with the cluster description and you will return the summary. 
-Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster: ```Members of this cluster can be described as:  relatively high on social and engaging,  normal on meticulous and inventive,  normal on humble and orderly,  normal on empathetic and concrete,  normal on self-possessed and systematic,  slightly high on planned and prepared,  relatively high on imaginative and conceptual,  slightly high on observant and routine,  normal on foresighted and cautious,  relatively high on unflappable and stable,  normal on kindly and warm,  relatively low on even temper´´´</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster: ```Members of this cluster can be described as:  relatively high on social and engaging,  extremely high on broad-minded and practical,  extremely high on exuberant and direct,  slightly low on intellectual and expressive,  extremely high on thoughtful and vigilant,  extremely high on planned and prepared,  normal on articulate and literal,  extremely low on speculative and spontaneous,  relatively high on foresighted and cautious,  normal on unflappable and stable,  normal on kindly and warm,  relatively high on variable temper´´´</t>
+Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster: ```Members of this cluster can be described as:  relatively high on engaging and sociable,  normal on thoughtful and imaginative,  slightly low on discreet and diligent,  normal on insightful and reserved,  slightly low on practical and grounded,  relatively high on organized and punctual´´´</t>
+  </si>
+  <si>
+    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster:  ```Members of this cluster can be described as:  relatively low on sensitive and private,  normal on thoughtful and imaginative,  normal on carefree and spontaneous,  normal on empathetic and considerate,  normal on not practical and speculative,  slightly low on disorganized and laid-back´´´</t>
+  </si>
+  <si>
+    <t>Members of this cluster can be described as naturally engaging and sociable, making them approachable and charming in various social settings. Their strengths lie in their ability to connect with others easily and their organizational skills, which suggest they can manage tasks effectively. However, they may struggle with being discreet and diligent at times, and their slightly lower practical orientation could hinder their ability to navigate certain real-world challenges effectively.</t>
+  </si>
+  <si>
+    <t>This cluster comprises individuals who display a balance of traits, showing an average level of creativity and spontaneity while being less sensitive and private. Their strengths lie in their empathetic and considerate nature, which allows for meaningful interactions with others, alongside a good level of thoughtfulness and imagination. However, they may struggle with aspects of their personal boundaries and occasional disorganization, indicating a somewhat relaxed stance that could lead to challenges in more structured environments.</t>
+  </si>
+  <si>
+    <t>This cluster is characterized by individuals who are vibrant and outgoing, displaying a strong sociability alongside a carefree attitude. Their specific strengths lie in their encouraging demeanor, empathy, and spontaneity, making them highly approachable and considerate of others' feelings. However, their extreme inclination towards being not practical and speculative may hinder their ability to focus on realistic goals and grounded decision-making.</t>
   </si>
   <si>
     <t>Those were really good. Exactly what I am looking for. 
@@ -225,14 +138,14 @@
 The first sentence should give an overview of the cluster. 
 The second sentence should describe the cluster’s specific strengths based on the available information.
 The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-Now do the same thing with the following: ```Members of this cluster can be described as:  relatively low on private and sensitive,  normal on broad-minded and practical,  relatively high on exuberant and direct,  slightly low on intellectual and expressive,  quite low on self-possessed and systematic,  normal on planned and prepared,  relatively high on imaginative and conceptual,  normal on speculative and spontaneous,  normal on impromptu and bold,  normal on unflappable and stable,  slightly low on kindly and warm,  slightly high on variable temper´´´</t>
+Now do the same thing with the following, here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster: ```Members of this cluster can be described as:  slightly high on engaging and sociable,  extremely high on not anxious and carefree,  extremely high on carefree and spontaneous,  very high on empathetic and considerate,  extremely high on not practical and speculative,  extremely high on organized and punctual´´´</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="20" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -370,12 +283,6 @@
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -721,16 +628,19 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1086,12 +996,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="88.7265625" customWidth="1"/>
-    <col min="2" max="2" width="94.90625" customWidth="1"/>
+    <col min="1" max="1" width="98" customWidth="1"/>
+    <col min="2" max="2" width="59.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -1102,244 +1012,124 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" ht="159" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="61.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" ht="120" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A25" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="130" x14ac:dyDescent="0.35">
-      <c r="A26" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="50" x14ac:dyDescent="0.35">
-      <c r="A27" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="50" x14ac:dyDescent="0.35">
-      <c r="A28" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="50" x14ac:dyDescent="0.35">
-      <c r="A29" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="60" x14ac:dyDescent="0.35">
-      <c r="A30" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="130" x14ac:dyDescent="0.35">
-      <c r="A31" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/data/describe/few_shot/cluster/messages_personality.xlsx
+++ b/data/describe/few_shot/cluster/messages_personality.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\cluster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0C869D-EFC7-4845-A54C-23BC3F23AE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F423108-9BBF-4DE7-98A9-C328B3BA6200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -121,15 +121,6 @@
     <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster:  ```Members of this cluster can be described as:  relatively low on sensitive and private,  normal on thoughtful and imaginative,  normal on carefree and spontaneous,  normal on empathetic and considerate,  normal on not practical and speculative,  slightly low on disorganized and laid-back´´´</t>
   </si>
   <si>
-    <t>Members of this cluster can be described as naturally engaging and sociable, making them approachable and charming in various social settings. Their strengths lie in their ability to connect with others easily and their organizational skills, which suggest they can manage tasks effectively. However, they may struggle with being discreet and diligent at times, and their slightly lower practical orientation could hinder their ability to navigate certain real-world challenges effectively.</t>
-  </si>
-  <si>
-    <t>This cluster comprises individuals who display a balance of traits, showing an average level of creativity and spontaneity while being less sensitive and private. Their strengths lie in their empathetic and considerate nature, which allows for meaningful interactions with others, alongside a good level of thoughtfulness and imagination. However, they may struggle with aspects of their personal boundaries and occasional disorganization, indicating a somewhat relaxed stance that could lead to challenges in more structured environments.</t>
-  </si>
-  <si>
-    <t>This cluster is characterized by individuals who are vibrant and outgoing, displaying a strong sociability alongside a carefree attitude. Their specific strengths lie in their encouraging demeanor, empathy, and spontaneity, making them highly approachable and considerate of others' feelings. However, their extreme inclination towards being not practical and speculative may hinder their ability to focus on realistic goals and grounded decision-making.</t>
-  </si>
-  <si>
     <t>Those were really good. Exactly what I am looking for. 
 Make sure you continue to use the same format and style in the next example. 
 I am now going to give you one last description task to complete. 
@@ -139,6 +130,15 @@
 The second sentence should describe the cluster’s specific strengths based on the available information.
 The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
 Now do the same thing with the following, here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster: ```Members of this cluster can be described as:  slightly high on engaging and sociable,  extremely high on not anxious and carefree,  extremely high on carefree and spontaneous,  very high on empathetic and considerate,  extremely high on not practical and speculative,  extremely high on organized and punctual´´´</t>
+  </si>
+  <si>
+    <t>These are individuals who thrive on social connection while maintaining a structured approach to their daily lives. Their primary strengths are their vibrant, engaging nature and their high level of organization, meaning they can lead conversations with ease and stick to a prepared schedule efficiently. However, they may struggle with a slight lack of diligence and a less grounded mindset, which could lead them to prioritize the excitement of the moment over practical, behind-the-scenes duties or long-term chores.</t>
+  </si>
+  <si>
+    <t>These individuals are a vibrant group that blends a high-spirited, carefree nature with a surprising knack for precision. Their specific strengths lie in their incredible emotional intelligence and ability to stay calm under pressure, fueled by a deeply empathetic mindset and a prepared, punctual approach to life. However, their extreme inclination toward speculative and spontaneous thinking suggests they may struggle with being grounded, often diving into abstract ideas or risking a lack of focus on the purely practical, day-to-day realities of their environment.</t>
+  </si>
+  <si>
+    <t>These individuals who navigate the world with a steady, reliable temperament. Their primary strengths lie in their resilient nature and an orderly approach to life, as their low levels of sensitivity and disorganization suggest they remain unfazed by irritation and stay prepared for what comes next. However, because they lean away from being private or laid-back, they may occasionally lack the quiet introspection or the easygoing flexibility needed to fully relax or shirk duties when the situation calls for a softer touch.</t>
   </si>
 </sst>
 </file>
@@ -628,13 +628,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1012,96 +1009,96 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="58" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2" ht="40" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="58" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="58" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="58" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="12" spans="1:2" ht="40" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="13" spans="1:2" ht="40" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -1109,26 +1106,26 @@
       </c>
     </row>
     <row r="14" spans="1:2" ht="159" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="61.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="120" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="61.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="120" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>30</v>
       </c>
     </row>

--- a/data/describe/few_shot/cluster/messages_personality.xlsx
+++ b/data/describe/few_shot/cluster/messages_personality.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\cluster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F423108-9BBF-4DE7-98A9-C328B3BA6200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D9D36AA-5A48-4014-9E1B-7DB412859343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="messages_personality1.xlsx" sheetId="1" r:id="rId1"/>
+    <sheet name="QandA_data" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>User</t>
   </si>
@@ -33,119 +33,95 @@
     <t>Assistant</t>
   </si>
   <si>
-    <t>What does it mean when a person is described as sensitive and private?</t>
-  </si>
-  <si>
-    <t>When a person is described as sensitive and private, they often aren't very interested in others and can easily get irritated. These individuals also tend to be quiet, prefer to keep in the background around strangers, and generally have little to say.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as engaging and sociable?</t>
-  </si>
-  <si>
-    <t>When a person is described as engaging and sociable, it means they feel very comfortable around others, often taking the lead to start conversations and chat with many different people at parties. They are genuinely interested in the people around them and frequently become the life of the party.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as thoughtful and imaginative?</t>
-  </si>
-  <si>
-    <t>A thoughtful and imaginative person tends to worry about things and can get stressed out easily, often because they possess a very vivid imagination. They are truly brimming with excellent ideas and are constantly full of new thoughts.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as not anxious and carefree?</t>
-  </si>
-  <si>
-    <t>A person described as not anxious and carefree isn't prone to worrying or getting stressed out easily. They also don't tend to have a vivid imagination, excellent ideas, or be constantly full of new thoughts, indicating a more relaxed and less preoccupied state.</t>
+    <t>What does it mean when a person is described as aloof and irritable?</t>
+  </si>
+  <si>
+    <t>When a person is described as aloof and irritable, it means they tend to be disinterested in others, often keeping to themselves and not engaging in conversation. They can be easily irritated and might come off as quiet or reserved around strangers, preferring to stay in the background and not share much about themselves.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as sociable and engaging?</t>
+  </si>
+  <si>
+    <t>When a person is described as sociable and engaging, it means they feel at ease in social settings and are eager to connect with others. They're the type who effortlessly strike up conversations, mingle with a variety of guests at gatherings, and often become the vibrant energy that lights up the party, showing genuine interest in the people around them.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as concerned and creative?</t>
+  </si>
+  <si>
+    <t>When a person is described as concerned and creative, it means they are deeply engaged with their thoughts and feelings, often worrying about various matters while also possessing a vivid imagination. They are likely to come up with excellent ideas and are brimming with creative potential, even as they may find themselves feeling stressed out by their own concerns.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as not concerned?</t>
+  </si>
+  <si>
+    <t>When a person is described as not concerned, it means they donâ€™t worry about things or get stressed out easily. Instead of being preoccupied with worries and bursting with ideas, they tend to approach life with a sense of calm and a steady mindset, allowing them to navigate challenges without the weight of anxiety.</t>
   </si>
   <si>
     <t>What does it mean when a person is described as discreet and diligent?</t>
   </si>
   <si>
-    <t>A discreet and diligent person strongly prefers to stay out of the limelight, making sure their chores are done right away, and always setting aside time for others. They also tend to be quiet when meeting new people and appreciate things being in their proper place.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as carefree and spontaneous?</t>
-  </si>
-  <si>
-    <t>A carefree and spontaneous person might occasionally insult others without much thought, and you'll often find their belongings scattered as they tend to forget putting things back or shirk their duties. However, they are also known for being the vibrant life of the party!</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as insightful and reserved?</t>
-  </si>
-  <si>
-    <t>A person described as insightful and reserved is often brimming with original thoughts and excellent ideas, often expressed with a rich vocabulary. While intellectually vibrant, they tend to keep to themselves, not showing much interest in other people's problems or feelings.</t>
+    <t>When a person is described as discreet and diligent, they often blend seamlessly into the background, preferring not to draw attention to themselves while getting things done efficiently and responsibly. They are attentive to the needs of others, take care of their obligations promptly, and maintain a sense of order, showcasing a thoughtful and reliable nature that reflects their quiet strength.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as vibrant and carefree?</t>
+  </si>
+  <si>
+    <t>When a person is described as vibrant and carefree, it means they have a lively and outgoing personality, often bringing energy and fun to social situations as they embrace being the life of the party. However, this carefree disposition may also lead to some recklessness, as they might forget where they put things or neglect certain responsibilities along the way.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as ideas and self-focused?</t>
+  </si>
+  <si>
+    <t>When a person is described as ideas and self-focused, it often means they are brimming with creativity and new thoughts, showing a strong inclination for coming up with innovative ideas. However, they may not pay much attention to others, feeling less interest in other people's problems or emotions, which can make them seem a bit distant in social situations.</t>
   </si>
   <si>
     <t>What does it mean when a person is described as empathetic and considerate?</t>
   </si>
   <si>
-    <t>When someone is described as empathetic and considerate, it means they truly feel and sympathize with the emotions of those around them. They are also known for taking the time to be there for others, offering their support and understanding.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as practical and grounded?</t>
-  </si>
-  <si>
-    <t>A practical and grounded person isn't particularly interested in abstract ideas and may find them hard to grasp, often coupled with not having a very vivid imagination. You'll find them relaxed most of the time, and they're usually the ones to start conversations.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as not practical and speculative?</t>
-  </si>
-  <si>
-    <t>A person described as not practical and speculative is someone who loves to dive into abstract ideas and possesses a good imagination. They easily grasp complex concepts and may not always be relaxed, often preferring others to initiate conversations.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as disorganized and laid-back?</t>
-  </si>
-  <si>
-    <t>When you describe someone as disorganized and laid-back, imagine a person who often creates a bit of a mess, frequently forgets to put things away, and has a habit of leaving their belongings scattered. They might even shirk their duties from time to time, but you'll usually find them quite relaxed and easygoing.</t>
-  </si>
-  <si>
-    <t>What does it mean when a person is described as organized and punctual?</t>
-  </si>
-  <si>
-    <t>When a person is described as organized and punctual, it means they have a knack for getting things done efficiently, often completing chores right away and sticking to a schedule. They approach life with a prepared mindset, ensuring they are always ready for what comes next!</t>
-  </si>
-  <si>
-    <t>Thats really good. You truly understand the factors and names. 
-Now your task is to provide a description of a cluster.
-Please use the statistical description enclosed with ``` ´´´ . It provides information about the cluster based on the latent factors that most accurately describe it.
-Now your task is to provide a description of a cluster.
-You will receive information about the cluster based on the latent factors that best describe it.
-For each cluster, write a concise summary based on the available information.
-The first sentence should give an overview of the cluster. 
-The second sentence should describe the cluster’s specific strengths based on the available information.
-The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-I will provided you with the cluster description and you will return the summary. 
-Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster: ```Members of this cluster can be described as:  relatively high on engaging and sociable,  normal on thoughtful and imaginative,  slightly low on discreet and diligent,  normal on insightful and reserved,  slightly low on practical and grounded,  relatively high on organized and punctual´´´</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster:  ```Members of this cluster can be described as:  relatively low on sensitive and private,  normal on thoughtful and imaginative,  normal on carefree and spontaneous,  normal on empathetic and considerate,  normal on not practical and speculative,  slightly low on disorganized and laid-back´´´</t>
-  </si>
-  <si>
-    <t>Those were really good. Exactly what I am looking for. 
-Make sure you continue to use the same format and style in the next example. 
-I am now going to give you one last description task to complete. 
-You will receive information about the cluster based on the latent factors that best describe it.
-For each cluster, write a concise summary based on the available information.
-The first sentence should give an overview of the cluster. 
-The second sentence should describe the cluster’s specific strengths based on the available information.
-The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-Now do the same thing with the following, here is the cluster description based on the factor scores at the cluster center, representing a typical person in that cluster: ```Members of this cluster can be described as:  slightly high on engaging and sociable,  extremely high on not anxious and carefree,  extremely high on carefree and spontaneous,  very high on empathetic and considerate,  extremely high on not practical and speculative,  extremely high on organized and punctual´´´</t>
-  </si>
-  <si>
-    <t>These are individuals who thrive on social connection while maintaining a structured approach to their daily lives. Their primary strengths are their vibrant, engaging nature and their high level of organization, meaning they can lead conversations with ease and stick to a prepared schedule efficiently. However, they may struggle with a slight lack of diligence and a less grounded mindset, which could lead them to prioritize the excitement of the moment over practical, behind-the-scenes duties or long-term chores.</t>
-  </si>
-  <si>
-    <t>These individuals are a vibrant group that blends a high-spirited, carefree nature with a surprising knack for precision. Their specific strengths lie in their incredible emotional intelligence and ability to stay calm under pressure, fueled by a deeply empathetic mindset and a prepared, punctual approach to life. However, their extreme inclination toward speculative and spontaneous thinking suggests they may struggle with being grounded, often diving into abstract ideas or risking a lack of focus on the purely practical, day-to-day realities of their environment.</t>
-  </si>
-  <si>
-    <t>These individuals who navigate the world with a steady, reliable temperament. Their primary strengths lie in their resilient nature and an orderly approach to life, as their low levels of sensitivity and disorganization suggest they remain unfazed by irritation and stay prepared for what comes next. However, because they lean away from being private or laid-back, they may occasionally lack the quiet introspection or the easygoing flexibility needed to fully relax or shirk duties when the situation calls for a softer touch.</t>
+    <t>When a person is described as empathetic and considerate, it means they are in tune with the emotions of others, feeling what others feel and understanding their experiences. They also take the time to care for and support those around them, demonstrating kindness and thoughtfulness in their interactions.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as concrete and relaxed?</t>
+  </si>
+  <si>
+    <t>When a person is described as concrete and relaxed, it suggests they prefer straightforward ideas over complex concepts and generally maintain a calm demeanor. They may not engage much with imaginative thoughts and might find abstract notions challenging to grasp, lending to an overall sense of practicality and ease in their interactions.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as abstract and curious?</t>
+  </si>
+  <si>
+    <t>When a person is described as abstract and curious, they are not concrete and relaxed, indicating a vibrant imagination and a keen interest in exploring new ideas. They thrive on abstract thoughts and are always eager to discover and learn about the world around them, making them inquisitive and open-minded individuals.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as chaotic and forgetful?</t>
+  </si>
+  <si>
+    <t>When a person is described as chaotic and forgetful, it suggests that they tend to make a mess of things and often forget to put items back where they belong. This carefree attitude might lead them to leave their belongings scattered and even neglect their responsibilities, all while remaining pretty relaxed about the whole situation.</t>
+  </si>
+  <si>
+    <t>What does it mean when a person is described as organised and prompt?</t>
+  </si>
+  <si>
+    <t>When a person is described as organised and prompt, they are someone who values order and efficiency in their life. They make a habit of following a schedule, getting tasks done quickly, and always being ready for what lies ahead.</t>
+  </si>
+  <si>
+    <t>From your answers I see that you have all the information you need about the factors. We are now going to do the most important task: provide a description of a cluster. Make sure you continue to use the same format and style as in earlier examples. This is the last description task to complete, so please pay close attention. You will receive information about the cluster based on the latent factors that best describe it. For each cluster, write a concise summary based on the available information. The first sentence should give an overview of the cluster. The second sentence should describe the cluster’s specific strengths based on the available information, if any exists. The third sentence should describe the cluster’s specific weaknesses based on the available information, if any exists. Now do this task based on the following description: ```Members of this cluster can be described as: slightly low on aloof and irritable, normal on concerned and creative, relatively low on discreet and diligent, normal on empathetic and considerate, relatively high on abstract and curious, relatively low on chaotic and forgetful´´´</t>
+  </si>
+  <si>
+    <t>These individuals who exhibit a balanced personality, showing moderate traits in various areas. They have a strength in being abstract and curious, which suggests an openness to new ideas and creativity, along with an ability to empathize and be considerate towards others. However, they may experience weaknesses in their discretion and diligence, which could pose challenges in situations requiring focus and reliability.</t>
+  </si>
+  <si>
+    <t>These individuals who are predominantly sociable and engaging, exuding a vibrant and carefree aura. Their strengths lie in their ability to connect with others and maintain an uplifting energy, which fosters positive interactions. However, they may face challenges due to their slight lack of concern and creativity, potentially hindering their ability to address deeper issues and think outside the box.</t>
+  </si>
+  <si>
+    <t>Now do this task based on the following description: ```Members of this cluster can be described as: relatively high on sociable and engaging, slightly low on concerned and creative, quite high on vibrant and carefree, slightly low on ideas and self-focused, slightly high on abstract and curious, quite low on chaotic and forgetful´´´</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,12 +255,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -628,16 +598,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -994,139 +958,131 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="98" customWidth="1"/>
-    <col min="2" max="2" width="59.453125" customWidth="1"/>
+    <col min="1" max="1" width="76.7265625" customWidth="1"/>
+    <col min="2" max="2" width="88.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="40" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="40" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="40" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="159" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:2" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="61.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="120" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
